--- a/artfynd/A 33625-2022 artfynd.xlsx
+++ b/artfynd/A 33625-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6849469</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -862,8 +872,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6850301</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 33625-2022 artfynd.xlsx
+++ b/artfynd/A 33625-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,6 +875,239 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6850301</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136338282</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58092</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Utsikten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>411073</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7016976</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136338282</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136337503</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Utsikten, Utsikten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>410894</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7017040</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136337503</t>
         </is>
       </c>
     </row>
@@ -882,6 +1115,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33625-2022 artfynd.xlsx
+++ b/artfynd/A 33625-2022 artfynd.xlsx
@@ -883,7 +883,7 @@
         <v>136338282</v>
       </c>
       <c r="B4" t="n">
-        <v>58092</v>
+        <v>58097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136337503</v>
       </c>
       <c r="B5" t="n">
-        <v>79455</v>
+        <v>79461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33625-2022 artfynd.xlsx
+++ b/artfynd/A 33625-2022 artfynd.xlsx
@@ -883,7 +883,7 @@
         <v>136338282</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>58110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136337503</v>
       </c>
       <c r="B5" t="n">
-        <v>79461</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33625-2022 artfynd.xlsx
+++ b/artfynd/A 33625-2022 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>136337503</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79475</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
